--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH271"/>
+  <dimension ref="A1:AH274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29557,7 +29557,7 @@
         <v>371.43</v>
       </c>
       <c r="I271" t="n">
-        <v>385.52</v>
+        <v>389.29</v>
       </c>
       <c r="J271" t="n">
         <v>378.53</v>
@@ -29629,9 +29629,333 @@
         <v>395.6</v>
       </c>
       <c r="AG271" t="n">
-        <v>376.79</v>
+        <v>377.59</v>
       </c>
       <c r="AH271" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>369.66</v>
+      </c>
+      <c r="C272" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="D272" t="n">
+        <v>361.41</v>
+      </c>
+      <c r="E272" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="F272" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="G272" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="H272" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="I272" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="J272" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="K272" t="n">
+        <v>381.35</v>
+      </c>
+      <c r="L272" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="M272" t="n">
+        <v>385.58</v>
+      </c>
+      <c r="N272" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="O272" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="P272" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="R272" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="S272" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="T272" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="U272" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="V272" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="W272" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="X272" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>394.31</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="C273" t="n">
+        <v>363.97</v>
+      </c>
+      <c r="D273" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="E273" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="F273" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="G273" t="n">
+        <v>360.78</v>
+      </c>
+      <c r="H273" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="I273" t="n">
+        <v>390.56</v>
+      </c>
+      <c r="J273" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="K273" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="L273" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="M273" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="N273" t="n">
+        <v>382.48</v>
+      </c>
+      <c r="O273" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="P273" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>378.14</v>
+      </c>
+      <c r="R273" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="S273" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="T273" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="U273" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="V273" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="W273" t="n">
+        <v>378.13</v>
+      </c>
+      <c r="X273" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>377.66</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>384</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>386.75</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>376.29</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="C274" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="D274" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="E274" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="F274" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="G274" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="H274" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="I274" t="n">
+        <v>391.74</v>
+      </c>
+      <c r="J274" t="n">
+        <v>375.86</v>
+      </c>
+      <c r="K274" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="L274" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="M274" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="N274" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="O274" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="P274" t="n">
+        <v>376.12</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="R274" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="S274" t="n">
+        <v>376.98</v>
+      </c>
+      <c r="T274" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="U274" t="n">
+        <v>377.22</v>
+      </c>
+      <c r="V274" t="n">
+        <v>374.86</v>
+      </c>
+      <c r="W274" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="X274" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>384</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>394.2</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="AH274" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29648,7 +29972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32421,6 +32745,36 @@
       </c>
       <c r="B277" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -32589,28 +32943,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1669299888571913</v>
+        <v>-0.1847279624015164</v>
       </c>
       <c r="J2" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K2" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03164521153508915</v>
+        <v>0.03873379725059478</v>
       </c>
       <c r="M2" t="n">
-        <v>5.544804805960147</v>
+        <v>5.582199555205111</v>
       </c>
       <c r="N2" t="n">
-        <v>47.18819435989133</v>
+        <v>47.44256783095797</v>
       </c>
       <c r="O2" t="n">
-        <v>6.869366372518744</v>
+        <v>6.887856548372503</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2547158215299</v>
+        <v>380.451622162326</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32667,28 +33021,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2317588051657254</v>
+        <v>-0.2397253372284192</v>
       </c>
       <c r="J3" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05855799470948608</v>
+        <v>0.06358131870745232</v>
       </c>
       <c r="M3" t="n">
-        <v>5.492948866107559</v>
+        <v>5.469691094195482</v>
       </c>
       <c r="N3" t="n">
-        <v>48.45358547222926</v>
+        <v>48.07063542286598</v>
       </c>
       <c r="O3" t="n">
-        <v>6.960860972051464</v>
+        <v>6.933299028807713</v>
       </c>
       <c r="P3" t="n">
-        <v>374.1246460063974</v>
+        <v>374.2119592525434</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32745,28 +33099,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3684081079230943</v>
+        <v>-0.3687491215535234</v>
       </c>
       <c r="J4" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K4" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09813170663584769</v>
+        <v>0.1003903434695319</v>
       </c>
       <c r="M4" t="n">
-        <v>6.452227817540248</v>
+        <v>6.386150476870858</v>
       </c>
       <c r="N4" t="n">
-        <v>69.02878917778898</v>
+        <v>68.26112891734589</v>
       </c>
       <c r="O4" t="n">
-        <v>8.30835658706275</v>
+        <v>8.262029346192488</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7515642753612</v>
+        <v>370.755348569888</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32823,28 +33177,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6098286641762579</v>
+        <v>-0.6233064465338954</v>
       </c>
       <c r="J5" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1649733151046497</v>
+        <v>0.1738438765802168</v>
       </c>
       <c r="M5" t="n">
-        <v>7.859345579886229</v>
+        <v>7.832739049782752</v>
       </c>
       <c r="N5" t="n">
-        <v>103.6217295041393</v>
+        <v>102.8855812369648</v>
       </c>
       <c r="O5" t="n">
-        <v>10.17947589535627</v>
+        <v>10.14325299087846</v>
       </c>
       <c r="P5" t="n">
-        <v>384.5733265823528</v>
+        <v>384.7231011416409</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32901,28 +33255,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5688863368729349</v>
+        <v>-0.5827120498752595</v>
       </c>
       <c r="J6" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K6" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1132313260348826</v>
+        <v>0.1202628025795405</v>
       </c>
       <c r="M6" t="n">
-        <v>9.200259442996575</v>
+        <v>9.165111154308933</v>
       </c>
       <c r="N6" t="n">
-        <v>140.6833923873274</v>
+        <v>139.5728731095262</v>
       </c>
       <c r="O6" t="n">
-        <v>11.86100300932967</v>
+        <v>11.81409637295744</v>
       </c>
       <c r="P6" t="n">
-        <v>383.410964991054</v>
+        <v>383.5634520500877</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32979,28 +33333,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6835222476161795</v>
+        <v>-0.6919526585712001</v>
       </c>
       <c r="J7" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K7" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05533957664990197</v>
+        <v>0.05787363227337017</v>
       </c>
       <c r="M7" t="n">
-        <v>16.61783465522402</v>
+        <v>16.48325159428202</v>
       </c>
       <c r="N7" t="n">
-        <v>439.6907145201912</v>
+        <v>434.990641985091</v>
       </c>
       <c r="O7" t="n">
-        <v>20.96880336404992</v>
+        <v>20.85642927217147</v>
       </c>
       <c r="P7" t="n">
-        <v>383.5076455915167</v>
+        <v>383.6011846715919</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33061,28 +33415,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.449366645861092</v>
+        <v>0.4361339627683004</v>
       </c>
       <c r="J8" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K8" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03128434411469483</v>
+        <v>0.03016467062886385</v>
       </c>
       <c r="M8" t="n">
-        <v>14.57535432240405</v>
+        <v>14.46798125307077</v>
       </c>
       <c r="N8" t="n">
-        <v>347.7919127935432</v>
+        <v>344.2648217484517</v>
       </c>
       <c r="O8" t="n">
-        <v>18.64917994962629</v>
+        <v>18.55437473342747</v>
       </c>
       <c r="P8" t="n">
-        <v>364.1909855515411</v>
+        <v>364.337519757984</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33143,28 +33497,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6353513321522682</v>
+        <v>0.6453393423556514</v>
       </c>
       <c r="J9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K9" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1246231729034092</v>
+        <v>0.1305892284502216</v>
       </c>
       <c r="M9" t="n">
-        <v>9.928268970220012</v>
+        <v>9.862989749287232</v>
       </c>
       <c r="N9" t="n">
-        <v>161.16280953526</v>
+        <v>159.4869078694673</v>
       </c>
       <c r="O9" t="n">
-        <v>12.69499151379236</v>
+        <v>12.62881260726705</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2361164638808</v>
+        <v>370.1275078665876</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33225,28 +33579,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4097000094681671</v>
+        <v>0.3932620003014962</v>
       </c>
       <c r="J10" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K10" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1096101634712709</v>
+        <v>0.1032203581706129</v>
       </c>
       <c r="M10" t="n">
-        <v>6.87133558548022</v>
+        <v>6.871390331346687</v>
       </c>
       <c r="N10" t="n">
-        <v>77.2998825642084</v>
+        <v>77.10392600763721</v>
       </c>
       <c r="O10" t="n">
-        <v>8.792035177602989</v>
+        <v>8.780884124485256</v>
       </c>
       <c r="P10" t="n">
-        <v>373.1098760744332</v>
+        <v>373.2884318568724</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33303,28 +33657,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3730526115037295</v>
+        <v>0.3657895331133009</v>
       </c>
       <c r="J11" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K11" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1212880169059463</v>
+        <v>0.1193608092873676</v>
       </c>
       <c r="M11" t="n">
-        <v>5.992626835078831</v>
+        <v>5.959092339034822</v>
       </c>
       <c r="N11" t="n">
-        <v>55.94515211296563</v>
+        <v>55.45223377271601</v>
       </c>
       <c r="O11" t="n">
-        <v>7.47964919718603</v>
+        <v>7.446625663528146</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9524744512332</v>
+        <v>374.0326024503076</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33381,28 +33735,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4074737240205467</v>
+        <v>0.3931762298136771</v>
       </c>
       <c r="J12" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K12" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1470411799543323</v>
+        <v>0.1400168809460481</v>
       </c>
       <c r="M12" t="n">
-        <v>5.905924893805241</v>
+        <v>5.910527496080438</v>
       </c>
       <c r="N12" t="n">
-        <v>53.44190595067515</v>
+        <v>53.3340149370576</v>
       </c>
       <c r="O12" t="n">
-        <v>7.310397113062679</v>
+        <v>7.303014099469999</v>
       </c>
       <c r="P12" t="n">
-        <v>371.4839513698316</v>
+        <v>371.6416706413037</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33459,28 +33813,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3130531467745455</v>
+        <v>0.3141497348129139</v>
       </c>
       <c r="J13" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K13" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214627949800369</v>
+        <v>0.1247106390819421</v>
       </c>
       <c r="M13" t="n">
-        <v>5.019352004400647</v>
+        <v>4.974276447684453</v>
       </c>
       <c r="N13" t="n">
-        <v>39.33205801612628</v>
+        <v>38.90825762256333</v>
       </c>
       <c r="O13" t="n">
-        <v>6.27152756640089</v>
+        <v>6.237648404852853</v>
       </c>
       <c r="P13" t="n">
-        <v>375.2891330889327</v>
+        <v>375.27705644554</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33537,28 +33891,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.14100800325164</v>
+        <v>0.1421348378536361</v>
       </c>
       <c r="J14" t="n">
+        <v>273</v>
+      </c>
+      <c r="K14" t="n">
         <v>270</v>
       </c>
-      <c r="K14" t="n">
-        <v>267</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.0391831835558496</v>
+        <v>0.04068728053367365</v>
       </c>
       <c r="M14" t="n">
-        <v>4.19526932641955</v>
+        <v>4.155299667812246</v>
       </c>
       <c r="N14" t="n">
-        <v>27.21969902496007</v>
+        <v>26.92075139633595</v>
       </c>
       <c r="O14" t="n">
-        <v>5.217250140156217</v>
+        <v>5.188521118424396</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0156471990962</v>
+        <v>378.003283649472</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33615,28 +33969,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2779681241652838</v>
+        <v>0.2699379299616687</v>
       </c>
       <c r="J15" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K15" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1676513800482173</v>
+        <v>0.1617737256479438</v>
       </c>
       <c r="M15" t="n">
-        <v>3.700559653963178</v>
+        <v>3.686880686387553</v>
       </c>
       <c r="N15" t="n">
-        <v>21.87169780214652</v>
+        <v>21.7899051220455</v>
       </c>
       <c r="O15" t="n">
-        <v>4.67671870034392</v>
+        <v>4.667965844138696</v>
       </c>
       <c r="P15" t="n">
-        <v>374.0894727440389</v>
+        <v>374.1762638599384</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33693,28 +34047,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1654907582062269</v>
+        <v>0.1587780779552141</v>
       </c>
       <c r="J16" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K16" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08199989753624959</v>
+        <v>0.07717309013988904</v>
       </c>
       <c r="M16" t="n">
-        <v>3.482255932654551</v>
+        <v>3.472446513172829</v>
       </c>
       <c r="N16" t="n">
-        <v>17.45166347837281</v>
+        <v>17.37043087389161</v>
       </c>
       <c r="O16" t="n">
-        <v>4.177518818434312</v>
+        <v>4.167784888150011</v>
       </c>
       <c r="P16" t="n">
-        <v>374.8016488710452</v>
+        <v>374.8741875076656</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33771,28 +34125,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1994283590880423</v>
+        <v>0.1996652701841915</v>
       </c>
       <c r="J17" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K17" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1070739753460962</v>
+        <v>0.1095510095983026</v>
       </c>
       <c r="M17" t="n">
-        <v>3.464755255498189</v>
+        <v>3.428010996486897</v>
       </c>
       <c r="N17" t="n">
-        <v>18.87840522314316</v>
+        <v>18.67122758676692</v>
       </c>
       <c r="O17" t="n">
-        <v>4.344928678717657</v>
+        <v>4.32102159063883</v>
       </c>
       <c r="P17" t="n">
-        <v>372.4773340995496</v>
+        <v>372.474773630602</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33849,28 +34203,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.133290573485783</v>
+        <v>0.1265085924514806</v>
       </c>
       <c r="J18" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K18" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04619329454120236</v>
+        <v>0.04252285076793449</v>
       </c>
       <c r="M18" t="n">
-        <v>3.662222591020118</v>
+        <v>3.648934035149736</v>
       </c>
       <c r="N18" t="n">
-        <v>20.880467848058</v>
+        <v>20.76448881594019</v>
       </c>
       <c r="O18" t="n">
-        <v>4.569515056114598</v>
+        <v>4.556806866210175</v>
       </c>
       <c r="P18" t="n">
-        <v>374.4544205149553</v>
+        <v>374.527705116151</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33927,28 +34281,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1353546391273588</v>
+        <v>0.1279608515703586</v>
       </c>
       <c r="J19" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K19" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04432137865198971</v>
+        <v>0.04046503063627815</v>
       </c>
       <c r="M19" t="n">
-        <v>3.691245851931879</v>
+        <v>3.669947488157033</v>
       </c>
       <c r="N19" t="n">
-        <v>22.48561751684237</v>
+        <v>22.37228418237111</v>
       </c>
       <c r="O19" t="n">
-        <v>4.741900201063111</v>
+        <v>4.729934902551103</v>
       </c>
       <c r="P19" t="n">
-        <v>376.8214605073709</v>
+        <v>376.9013606514897</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34005,28 +34359,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1031192392532587</v>
+        <v>0.09348466919154165</v>
       </c>
       <c r="J20" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K20" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02747408289139741</v>
+        <v>0.02297218193120842</v>
       </c>
       <c r="M20" t="n">
-        <v>3.648538396972704</v>
+        <v>3.646118876530204</v>
       </c>
       <c r="N20" t="n">
-        <v>21.42482577065721</v>
+        <v>21.41709800383609</v>
       </c>
       <c r="O20" t="n">
-        <v>4.628695903886667</v>
+        <v>4.627861061423094</v>
       </c>
       <c r="P20" t="n">
-        <v>377.861413442088</v>
+        <v>377.9655344769972</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34083,28 +34437,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1541535883370289</v>
+        <v>0.1507306447503987</v>
       </c>
       <c r="J21" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K21" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05871790043976322</v>
+        <v>0.05746126444730693</v>
       </c>
       <c r="M21" t="n">
-        <v>3.64009346509699</v>
+        <v>3.614712642685543</v>
       </c>
       <c r="N21" t="n">
-        <v>21.6828555754457</v>
+        <v>21.47347314458468</v>
       </c>
       <c r="O21" t="n">
-        <v>4.656485324302622</v>
+        <v>4.633947900503919</v>
       </c>
       <c r="P21" t="n">
-        <v>374.8103482013818</v>
+        <v>374.8473407999338</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34161,28 +34515,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.208377758061485</v>
+        <v>0.1988566432755065</v>
       </c>
       <c r="J22" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K22" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08938985143231826</v>
+        <v>0.08315561830142126</v>
       </c>
       <c r="M22" t="n">
-        <v>4.064397676476082</v>
+        <v>4.062751675603462</v>
       </c>
       <c r="N22" t="n">
-        <v>25.17716994636675</v>
+        <v>25.12229957342794</v>
       </c>
       <c r="O22" t="n">
-        <v>5.017685716180991</v>
+        <v>5.012215036630805</v>
       </c>
       <c r="P22" t="n">
-        <v>373.9465080191769</v>
+        <v>374.0494000945686</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34239,28 +34593,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1917865137133296</v>
+        <v>0.1837286385032824</v>
       </c>
       <c r="J23" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K23" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08299732885729372</v>
+        <v>0.0778598564557762</v>
       </c>
       <c r="M23" t="n">
-        <v>3.911001383262452</v>
+        <v>3.907896535817546</v>
       </c>
       <c r="N23" t="n">
-        <v>23.13143271750169</v>
+        <v>23.03627180709034</v>
       </c>
       <c r="O23" t="n">
-        <v>4.809514811028415</v>
+        <v>4.79961163086039</v>
       </c>
       <c r="P23" t="n">
-        <v>376.7668171684106</v>
+        <v>376.8538976579936</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34317,28 +34671,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1814356657231627</v>
+        <v>0.1728847546651045</v>
       </c>
       <c r="J24" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K24" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06539837158710027</v>
+        <v>0.06067532564602351</v>
       </c>
       <c r="M24" t="n">
-        <v>4.105995052600007</v>
+        <v>4.102110422203983</v>
       </c>
       <c r="N24" t="n">
-        <v>26.77718027390274</v>
+        <v>26.66196545886035</v>
       </c>
       <c r="O24" t="n">
-        <v>5.174667165519222</v>
+        <v>5.163522582390858</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5642322636924</v>
+        <v>376.6566393096201</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34395,28 +34749,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1734878407465474</v>
+        <v>0.1662066464774155</v>
       </c>
       <c r="J25" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K25" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06254876613092042</v>
+        <v>0.05870224411363412</v>
       </c>
       <c r="M25" t="n">
-        <v>3.979955453821684</v>
+        <v>3.969118482937748</v>
       </c>
       <c r="N25" t="n">
-        <v>25.67603387793378</v>
+        <v>25.52373599032838</v>
       </c>
       <c r="O25" t="n">
-        <v>5.067152442736826</v>
+        <v>5.05210213577758</v>
       </c>
       <c r="P25" t="n">
-        <v>376.4172472252523</v>
+        <v>376.4959342352543</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34473,28 +34827,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1462251900641235</v>
+        <v>0.1460573641360357</v>
       </c>
       <c r="J26" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K26" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L26" t="n">
-        <v>0.052791944541418</v>
+        <v>0.05384966575107852</v>
       </c>
       <c r="M26" t="n">
-        <v>3.68871718488098</v>
+        <v>3.650503744101566</v>
       </c>
       <c r="N26" t="n">
-        <v>21.83644978275273</v>
+        <v>21.597287195758</v>
       </c>
       <c r="O26" t="n">
-        <v>4.67294872460128</v>
+        <v>4.647288155016644</v>
       </c>
       <c r="P26" t="n">
-        <v>380.4997063001401</v>
+        <v>380.5015244945342</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34551,28 +34905,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1007761222881867</v>
+        <v>0.09349499611264889</v>
       </c>
       <c r="J27" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K27" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02416323563376976</v>
+        <v>0.02123212707524635</v>
       </c>
       <c r="M27" t="n">
-        <v>3.860869072623595</v>
+        <v>3.849585598551799</v>
       </c>
       <c r="N27" t="n">
-        <v>23.34518350896241</v>
+        <v>23.21871000599354</v>
       </c>
       <c r="O27" t="n">
-        <v>4.831685369409147</v>
+        <v>4.818579666872131</v>
       </c>
       <c r="P27" t="n">
-        <v>381.0118278643434</v>
+        <v>381.0905144028911</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34629,28 +34983,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1405542568638791</v>
+        <v>0.1350208820312352</v>
       </c>
       <c r="J28" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K28" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03622743322516031</v>
+        <v>0.03420413188843263</v>
       </c>
       <c r="M28" t="n">
-        <v>4.462916299360028</v>
+        <v>4.433624088192639</v>
       </c>
       <c r="N28" t="n">
-        <v>29.91471851379179</v>
+        <v>29.66086436271538</v>
       </c>
       <c r="O28" t="n">
-        <v>5.469434935511327</v>
+        <v>5.446178877223496</v>
       </c>
       <c r="P28" t="n">
-        <v>382.849190836199</v>
+        <v>382.9089873313376</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34707,28 +35061,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1717838521650768</v>
+        <v>0.1620811957984463</v>
       </c>
       <c r="J29" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K29" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05790636594401688</v>
+        <v>0.05261151688708499</v>
       </c>
       <c r="M29" t="n">
-        <v>4.322426332573668</v>
+        <v>4.319558366770178</v>
       </c>
       <c r="N29" t="n">
-        <v>27.32702485276305</v>
+        <v>27.25760492470136</v>
       </c>
       <c r="O29" t="n">
-        <v>5.227525691258059</v>
+        <v>5.220881623318169</v>
       </c>
       <c r="P29" t="n">
-        <v>386.9021823925397</v>
+        <v>387.0070306221156</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34785,28 +35139,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1918707137795344</v>
+        <v>0.180902879741553</v>
       </c>
       <c r="J30" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K30" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L30" t="n">
-        <v>0.09560032700588061</v>
+        <v>0.08655319426319941</v>
       </c>
       <c r="M30" t="n">
-        <v>3.538472371442509</v>
+        <v>3.542928711688016</v>
       </c>
       <c r="N30" t="n">
-        <v>19.82340800347614</v>
+        <v>19.90060467820871</v>
       </c>
       <c r="O30" t="n">
-        <v>4.45234859411032</v>
+        <v>4.461009378852359</v>
       </c>
       <c r="P30" t="n">
-        <v>384.8416250023385</v>
+        <v>384.9601444740022</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34863,28 +35217,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1373825763869402</v>
+        <v>0.1203873764688665</v>
       </c>
       <c r="J31" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K31" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04631403668859813</v>
+        <v>0.03565665436844789</v>
       </c>
       <c r="M31" t="n">
-        <v>3.835081654479541</v>
+        <v>3.866296460444822</v>
       </c>
       <c r="N31" t="n">
-        <v>22.12157207184366</v>
+        <v>22.58541879382191</v>
       </c>
       <c r="O31" t="n">
-        <v>4.703357531789782</v>
+        <v>4.752411892273428</v>
       </c>
       <c r="P31" t="n">
-        <v>383.7512944996889</v>
+        <v>383.9349523470549</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34941,28 +35295,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1861765647558328</v>
+        <v>0.1733506590762699</v>
       </c>
       <c r="J32" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K32" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0763840888913041</v>
+        <v>0.06730131921673077</v>
       </c>
       <c r="M32" t="n">
-        <v>3.799545161331268</v>
+        <v>3.818834596388358</v>
       </c>
       <c r="N32" t="n">
-        <v>23.85604508698677</v>
+        <v>23.99628052830046</v>
       </c>
       <c r="O32" t="n">
-        <v>4.884265050853278</v>
+        <v>4.898599853866455</v>
       </c>
       <c r="P32" t="n">
-        <v>395.4389617983194</v>
+        <v>395.5775663303314</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35019,28 +35373,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1232321774193578</v>
+        <v>0.1126366034091789</v>
       </c>
       <c r="J33" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K33" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01979053410589482</v>
+        <v>0.01686169719623698</v>
       </c>
       <c r="M33" t="n">
-        <v>4.76043228811345</v>
+        <v>4.763683688875945</v>
       </c>
       <c r="N33" t="n">
-        <v>42.81239660469705</v>
+        <v>42.62334925425426</v>
       </c>
       <c r="O33" t="n">
-        <v>6.543118263083517</v>
+        <v>6.528656006733258</v>
       </c>
       <c r="P33" t="n">
-        <v>378.0540459671916</v>
+        <v>378.1685725658839</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35078,7 +35432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH271"/>
+  <dimension ref="A1:AH274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81312,7 +81666,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>-36.59305200159465,175.52289744578582</t>
+          <t>-36.593046271357345,175.52293896297766</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -81432,10 +81786,526 @@
       </c>
       <c r="AG271" t="inlineStr">
         <is>
-          <t>-36.603513086955076,175.53784856077914</t>
+          <t>-36.603506524839595,175.53784486358174</t>
         </is>
       </c>
       <c r="AH271" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-36.588730567721036,175.52479607396907</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>-36.58911581805779,175.52404185332406</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-36.58965704947698,175.52346670576168</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-36.59025190934913,175.52296792148158</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-36.590947568085774,175.52274493586853</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-36.59164707175682,175.52252800243295</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-36.59236364157263,175.5227093481347</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-36.593044629801334,175.52295085649553</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-36.59374215764848,175.52302966428576</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-36.59440041048134,175.52334951363102</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-36.595063204755775,175.52366335860785</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-36.595655207637414,175.5241522456484</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-36.59626406213255,175.52459294222368</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-36.59686284314133,175.52507026875483</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-36.59740996354269,175.5256367067467</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-36.597920207086396,175.52626613235077</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>-36.59847750417309,175.52684068265515</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>-36.59899117898332,175.52746383884838</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>-36.59949715808662,175.52809202901707</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>-36.599974671451044,175.52876035664727</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>-36.60047849345636,175.52940439664818</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>-36.600940454909825,175.5300837579826</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>-36.60138295311707,175.5307751334633</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>-36.60179310023832,175.5315083226421</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>-36.60215133284685,175.53227598870916</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>-36.60253816213384,175.53301845299794</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>-36.60285382484835,175.5338151590421</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>-36.60313440959682,175.53461306409906</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>-36.60336808194526,175.53543263193453</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>-36.603593321188455,175.5362792831765</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>-36.603626614092185,175.5370607489136</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>-36.6035228481016,175.53785406036144</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-36.58871446097705,175.52478099600157</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>-36.589109463466855,175.52403393365748</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-36.5896534849384,175.52346039013764</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-36.59025169688069,175.52296730509633</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-36.59094827756164,175.52274920334122</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-36.59164849235641,175.522556773511</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-36.592364598698296,175.52268826536556</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-36.593044341008955,175.5229529488736</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-36.593742946353444,175.52302657533832</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-36.594401800968456,175.5233452697105</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-36.59506591035999,175.52365666681882</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-36.595661873014876,175.52413831220906</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-36.59626427074312,175.52459257779248</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-36.59685968686825,175.52507500608118</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-36.597407384117794,175.52564014023017</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-36.597918530613505,175.52626831827186</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>-36.59847633153343,175.52684222923423</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>-36.59899009864034,175.5274651852798</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>-36.599499674551126,175.52808915017624</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>-36.599976693530365,175.52875813240047</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>-36.60047862826213,175.52940424836493</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>-36.60094122218364,175.53008298005562</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>-36.60138156093609,175.53077636874542</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>-36.601793770917375,175.5315077574719</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>-36.60215302093771,175.53227470045604</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>-36.602541807401,175.53301600769117</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>-36.6028535823327,175.53381530703197</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>-36.60313381988827,175.5346133413411</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>-36.6033655604527,175.53543348068254</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>-36.60358840821805,175.53628070650294</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>-36.60362553860031,175.53706061229894</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>-36.60351718827719,175.53785087152784</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-36.5886987856616,175.52476632191426</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>-36.58910558716609,175.5240291026615</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-36.58964873221973,175.52345196930648</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-36.59024812032816,175.5229569292789</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-36.59094505763147,175.52272983558117</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-36.59165048008286,175.52259703071823</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-36.592364598698296,175.52268826536556</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-36.59304254745545,175.52296594364236</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-36.59374446936971,175.52302061047413</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-36.594406379400624,175.5233312958248</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-36.59506970628173,175.52364727833782</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-36.59566674563468,175.52412812638286</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-36.59626640900153,175.52458884237254</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-36.5968583669722,175.52507698714481</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-36.59740805968147,175.5256392409845</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-36.597919896628454,175.52626653715097</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>-36.59847312220375,175.52684646197676</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>-36.598990162189935,175.52746510607795</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>-36.599501330119836,175.5280872562019</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>-36.59997682833565,175.52875798411736</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>-36.60048004372282,175.52940269139052</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>-36.60094303573992,175.53008114131907</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>-36.60138412547997,175.53077409322566</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>-36.60179555939492,175.53150625035127</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>-36.60215609019381,175.53227235817755</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>-36.602541173441516,175.53301643296192</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>-36.6028535823327,175.53381530703197</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>-36.60312986041656,175.5346152028233</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>-36.60336225642798,175.53543459283506</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>-36.603591478824555,175.53627981692392</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>-36.60362759995974,175.53706087414372</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>-36.60351792651516,175.53785128746262</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH274"/>
+  <dimension ref="A1:AH275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29878,7 +29878,7 @@
         <v>364.39</v>
       </c>
       <c r="H274" t="n">
-        <v>369.54</v>
+        <v>373.64</v>
       </c>
       <c r="I274" t="n">
         <v>391.74</v>
@@ -29958,6 +29958,114 @@
       <c r="AH274" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="C275" t="n">
+        <v>362.49</v>
+      </c>
+      <c r="D275" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="E275" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="F275" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="G275" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="H275" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="I275" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="J275" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="K275" t="n">
+        <v>378.64</v>
+      </c>
+      <c r="L275" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="M275" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="N275" t="n">
+        <v>382.92</v>
+      </c>
+      <c r="O275" t="n">
+        <v>379.58</v>
+      </c>
+      <c r="P275" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="R275" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="S275" t="n">
+        <v>378.22</v>
+      </c>
+      <c r="T275" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="U275" t="n">
+        <v>378.27</v>
+      </c>
+      <c r="V275" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="W275" t="n">
+        <v>378.41</v>
+      </c>
+      <c r="X275" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>378.14</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>380.63</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>379.83</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>394.71</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>376.21</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29972,7 +30080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32775,6 +32883,16 @@
       </c>
       <c r="B280" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -32943,28 +33061,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1847279624015164</v>
+        <v>-0.192777130612898</v>
       </c>
       <c r="J2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03873379725059478</v>
+        <v>0.04194428618788526</v>
       </c>
       <c r="M2" t="n">
-        <v>5.582199555205111</v>
+        <v>5.607899131440972</v>
       </c>
       <c r="N2" t="n">
-        <v>47.44256783095797</v>
+        <v>47.74035009637576</v>
       </c>
       <c r="O2" t="n">
-        <v>6.887856548372503</v>
+        <v>6.909439202741114</v>
       </c>
       <c r="P2" t="n">
-        <v>380.451622162326</v>
+        <v>380.5408294606603</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33021,28 +33139,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2397253372284192</v>
+        <v>-0.2433920743908323</v>
       </c>
       <c r="J3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06358131870745232</v>
+        <v>0.0657509648353648</v>
       </c>
       <c r="M3" t="n">
-        <v>5.469691094195482</v>
+        <v>5.467341625549576</v>
       </c>
       <c r="N3" t="n">
-        <v>48.07063542286598</v>
+        <v>47.99296968721113</v>
       </c>
       <c r="O3" t="n">
-        <v>6.933299028807713</v>
+        <v>6.92769584257357</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2119592525434</v>
+        <v>374.2522193549098</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33099,28 +33217,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3687491215535234</v>
+        <v>-0.3699678262745729</v>
       </c>
       <c r="J4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K4" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1003903434695319</v>
+        <v>0.1016704682896091</v>
       </c>
       <c r="M4" t="n">
-        <v>6.386150476870858</v>
+        <v>6.368320072325582</v>
       </c>
       <c r="N4" t="n">
-        <v>68.26112891734589</v>
+        <v>68.01823957296433</v>
       </c>
       <c r="O4" t="n">
-        <v>8.262029346192488</v>
+        <v>8.247317113641522</v>
       </c>
       <c r="P4" t="n">
-        <v>370.755348569888</v>
+        <v>370.7688552270701</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33177,28 +33295,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6233064465338954</v>
+        <v>-0.6284925691143897</v>
       </c>
       <c r="J5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K5" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1738438765802168</v>
+        <v>0.1770737204312527</v>
       </c>
       <c r="M5" t="n">
-        <v>7.832739049782752</v>
+        <v>7.827341444086978</v>
       </c>
       <c r="N5" t="n">
-        <v>102.8855812369648</v>
+        <v>102.6973377392519</v>
       </c>
       <c r="O5" t="n">
-        <v>10.14325299087846</v>
+        <v>10.13396949567404</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7231011416409</v>
+        <v>384.780840562451</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33255,28 +33373,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5827120498752595</v>
+        <v>-0.5884180253244361</v>
       </c>
       <c r="J6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K6" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1202628025795405</v>
+        <v>0.1229785145478377</v>
       </c>
       <c r="M6" t="n">
-        <v>9.165111154308933</v>
+        <v>9.158793262384856</v>
       </c>
       <c r="N6" t="n">
-        <v>139.5728731095262</v>
+        <v>139.2950720005556</v>
       </c>
       <c r="O6" t="n">
-        <v>11.81409637295744</v>
+        <v>11.8023333286497</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5634520500877</v>
+        <v>383.626501390466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33333,28 +33451,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6919526585712001</v>
+        <v>-0.6910098208626974</v>
       </c>
       <c r="J7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K7" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05787363227337017</v>
+        <v>0.05814227441823439</v>
       </c>
       <c r="M7" t="n">
-        <v>16.48325159428202</v>
+        <v>16.42574336379369</v>
       </c>
       <c r="N7" t="n">
-        <v>434.990641985091</v>
+        <v>433.3740211553821</v>
       </c>
       <c r="O7" t="n">
-        <v>20.85642927217147</v>
+        <v>20.81763726159581</v>
       </c>
       <c r="P7" t="n">
-        <v>383.6011846715919</v>
+        <v>383.5906980064905</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33415,28 +33533,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4361339627683004</v>
+        <v>0.4417574239094302</v>
       </c>
       <c r="J8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K8" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03016467062886385</v>
+        <v>0.03116059142782623</v>
       </c>
       <c r="M8" t="n">
-        <v>14.46798125307077</v>
+        <v>14.41694323289631</v>
       </c>
       <c r="N8" t="n">
-        <v>344.2648217484517</v>
+        <v>342.8777512665547</v>
       </c>
       <c r="O8" t="n">
-        <v>18.55437473342747</v>
+        <v>18.5169584777456</v>
       </c>
       <c r="P8" t="n">
-        <v>364.337519757984</v>
+        <v>364.2751637512083</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33497,28 +33615,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6453393423556514</v>
+        <v>0.6491001145773249</v>
       </c>
       <c r="J9" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1305892284502216</v>
+        <v>0.1327069242904367</v>
       </c>
       <c r="M9" t="n">
-        <v>9.862989749287232</v>
+        <v>9.848503486620459</v>
       </c>
       <c r="N9" t="n">
-        <v>159.4869078694673</v>
+        <v>158.9991534164197</v>
       </c>
       <c r="O9" t="n">
-        <v>12.62881260726705</v>
+        <v>12.60948664365127</v>
       </c>
       <c r="P9" t="n">
-        <v>370.1275078665876</v>
+        <v>370.086482381261</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33579,28 +33697,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3932620003014962</v>
+        <v>0.3871041018829771</v>
       </c>
       <c r="J10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1032203581706129</v>
+        <v>0.1006841396775618</v>
       </c>
       <c r="M10" t="n">
-        <v>6.871390331346687</v>
+        <v>6.874829415025406</v>
       </c>
       <c r="N10" t="n">
-        <v>77.10392600763721</v>
+        <v>77.10722255897545</v>
       </c>
       <c r="O10" t="n">
-        <v>8.780884124485256</v>
+        <v>8.781071834290815</v>
       </c>
       <c r="P10" t="n">
-        <v>373.2884318568724</v>
+        <v>373.3554495242441</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33657,28 +33775,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3657895331133009</v>
+        <v>0.3620571883791854</v>
       </c>
       <c r="J11" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K11" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1193608092873676</v>
+        <v>0.1178235144690056</v>
       </c>
       <c r="M11" t="n">
-        <v>5.959092339034822</v>
+        <v>5.954110301018113</v>
       </c>
       <c r="N11" t="n">
-        <v>55.45223377271601</v>
+        <v>55.34910405083112</v>
       </c>
       <c r="O11" t="n">
-        <v>7.446625663528146</v>
+        <v>7.439697846742912</v>
       </c>
       <c r="P11" t="n">
-        <v>374.0326024503076</v>
+        <v>374.0738508106514</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33735,28 +33853,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3931762298136771</v>
+        <v>0.3877890591047973</v>
       </c>
       <c r="J12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K12" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1400168809460481</v>
+        <v>0.1371589884010735</v>
       </c>
       <c r="M12" t="n">
-        <v>5.910527496080438</v>
+        <v>5.91579666890244</v>
       </c>
       <c r="N12" t="n">
-        <v>53.3340149370576</v>
+        <v>53.34949974910959</v>
       </c>
       <c r="O12" t="n">
-        <v>7.303014099469999</v>
+        <v>7.30407418836293</v>
       </c>
       <c r="P12" t="n">
-        <v>371.6416706413037</v>
+        <v>371.7012074672036</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33813,28 +33931,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3141497348129139</v>
+        <v>0.3136166057377252</v>
       </c>
       <c r="J13" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K13" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1247106390819421</v>
+        <v>0.1251701478352502</v>
       </c>
       <c r="M13" t="n">
-        <v>4.974276447684453</v>
+        <v>4.95857831936241</v>
       </c>
       <c r="N13" t="n">
-        <v>38.90825762256333</v>
+        <v>38.76623918407044</v>
       </c>
       <c r="O13" t="n">
-        <v>6.237648404852853</v>
+        <v>6.226254025019412</v>
       </c>
       <c r="P13" t="n">
-        <v>375.27705644554</v>
+        <v>375.2829483718678</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33891,28 +34009,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1421348378536361</v>
+        <v>0.1428893091980658</v>
       </c>
       <c r="J14" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K14" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04068728053367365</v>
+        <v>0.04139862797263183</v>
       </c>
       <c r="M14" t="n">
-        <v>4.155299667812246</v>
+        <v>4.144380645068824</v>
       </c>
       <c r="N14" t="n">
-        <v>26.92075139633595</v>
+        <v>26.82562274306082</v>
       </c>
       <c r="O14" t="n">
-        <v>5.188521118424396</v>
+        <v>5.179345783307078</v>
       </c>
       <c r="P14" t="n">
-        <v>378.003283649472</v>
+        <v>377.9949873947357</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33969,28 +34087,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2699379299616687</v>
+        <v>0.2686288939334827</v>
       </c>
       <c r="J15" t="n">
+        <v>274</v>
+      </c>
+      <c r="K15" t="n">
         <v>273</v>
       </c>
-      <c r="K15" t="n">
-        <v>272</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1617737256479438</v>
+        <v>0.1614020298348058</v>
       </c>
       <c r="M15" t="n">
-        <v>3.686880686387553</v>
+        <v>3.677756746930231</v>
       </c>
       <c r="N15" t="n">
-        <v>21.7899051220455</v>
+        <v>21.7231376678248</v>
       </c>
       <c r="O15" t="n">
-        <v>4.667965844138696</v>
+        <v>4.660808692472241</v>
       </c>
       <c r="P15" t="n">
-        <v>374.1762638599384</v>
+        <v>374.1904406994901</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34047,28 +34165,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1587780779552141</v>
+        <v>0.1575298121436168</v>
       </c>
       <c r="J16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07717309013988904</v>
+        <v>0.07654335927935119</v>
       </c>
       <c r="M16" t="n">
-        <v>3.472446513172829</v>
+        <v>3.465028902786704</v>
       </c>
       <c r="N16" t="n">
-        <v>17.37043087389161</v>
+        <v>17.31886109884745</v>
       </c>
       <c r="O16" t="n">
-        <v>4.167784888150011</v>
+        <v>4.161593576846188</v>
       </c>
       <c r="P16" t="n">
-        <v>374.8741875076656</v>
+        <v>374.8877032304068</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34125,28 +34243,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1996652701841915</v>
+        <v>0.2006328419461929</v>
       </c>
       <c r="J17" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K17" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1095510095983026</v>
+        <v>0.1112084966022374</v>
       </c>
       <c r="M17" t="n">
-        <v>3.428010996486897</v>
+        <v>3.420921472519328</v>
       </c>
       <c r="N17" t="n">
-        <v>18.67122758676692</v>
+        <v>18.61018982075112</v>
       </c>
       <c r="O17" t="n">
-        <v>4.32102159063883</v>
+        <v>4.313952922871449</v>
       </c>
       <c r="P17" t="n">
-        <v>372.474773630602</v>
+        <v>372.4642971507162</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34203,28 +34321,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1265085924514806</v>
+        <v>0.1255495072255819</v>
       </c>
       <c r="J18" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K18" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04252285076793449</v>
+        <v>0.04219975625720063</v>
       </c>
       <c r="M18" t="n">
-        <v>3.648934035149736</v>
+        <v>3.639446640362716</v>
       </c>
       <c r="N18" t="n">
-        <v>20.76448881594019</v>
+        <v>20.69568731461187</v>
       </c>
       <c r="O18" t="n">
-        <v>4.556806866210175</v>
+        <v>4.549251291653592</v>
       </c>
       <c r="P18" t="n">
-        <v>374.527705116151</v>
+        <v>374.5380897072196</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34281,28 +34399,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1279608515703586</v>
+        <v>0.1264864019615998</v>
       </c>
       <c r="J19" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K19" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04046503063627815</v>
+        <v>0.03983586224232993</v>
       </c>
       <c r="M19" t="n">
-        <v>3.669947488157033</v>
+        <v>3.66082901248017</v>
       </c>
       <c r="N19" t="n">
-        <v>22.37228418237111</v>
+        <v>22.30713343829126</v>
       </c>
       <c r="O19" t="n">
-        <v>4.729934902551103</v>
+        <v>4.72304281563181</v>
       </c>
       <c r="P19" t="n">
-        <v>376.9013606514897</v>
+        <v>376.9173254018838</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34359,28 +34477,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09348466919154165</v>
+        <v>0.09087288170480658</v>
       </c>
       <c r="J20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02297218193120842</v>
+        <v>0.02184421011569793</v>
       </c>
       <c r="M20" t="n">
-        <v>3.646118876530204</v>
+        <v>3.643100591905931</v>
       </c>
       <c r="N20" t="n">
-        <v>21.41709800383609</v>
+        <v>21.39070575998541</v>
       </c>
       <c r="O20" t="n">
-        <v>4.627861061423094</v>
+        <v>4.625008730800992</v>
       </c>
       <c r="P20" t="n">
-        <v>377.9655344769972</v>
+        <v>377.9938138668526</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34437,28 +34555,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1507306447503987</v>
+        <v>0.1502815588250687</v>
       </c>
       <c r="J21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05746126444730693</v>
+        <v>0.05754547355257755</v>
       </c>
       <c r="M21" t="n">
-        <v>3.614712642685543</v>
+        <v>3.603422473008521</v>
       </c>
       <c r="N21" t="n">
-        <v>21.47347314458468</v>
+        <v>21.39663347288232</v>
       </c>
       <c r="O21" t="n">
-        <v>4.633947900503919</v>
+        <v>4.625649519027823</v>
       </c>
       <c r="P21" t="n">
-        <v>374.8473407999338</v>
+        <v>374.8522033226411</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34515,28 +34633,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1988566432755065</v>
+        <v>0.1963290918099213</v>
       </c>
       <c r="J22" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K22" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08315561830142126</v>
+        <v>0.08164900811564002</v>
       </c>
       <c r="M22" t="n">
-        <v>4.062751675603462</v>
+        <v>4.059255844659524</v>
       </c>
       <c r="N22" t="n">
-        <v>25.12229957342794</v>
+        <v>25.07909900078907</v>
       </c>
       <c r="O22" t="n">
-        <v>5.012215036630805</v>
+        <v>5.00790365330535</v>
       </c>
       <c r="P22" t="n">
-        <v>374.0494000945686</v>
+        <v>374.0767674104923</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34593,28 +34711,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1837286385032824</v>
+        <v>0.1813746587773797</v>
       </c>
       <c r="J23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0778598564557762</v>
+        <v>0.0764340119285345</v>
       </c>
       <c r="M23" t="n">
-        <v>3.907896535817546</v>
+        <v>3.905362630112517</v>
       </c>
       <c r="N23" t="n">
-        <v>23.03627180709034</v>
+        <v>22.99425378900881</v>
       </c>
       <c r="O23" t="n">
-        <v>4.79961163086039</v>
+        <v>4.795232401981036</v>
       </c>
       <c r="P23" t="n">
-        <v>376.8538976579936</v>
+        <v>376.8793856085711</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34671,28 +34789,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1728847546651045</v>
+        <v>0.1706960454309506</v>
       </c>
       <c r="J24" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K24" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06067532564602351</v>
+        <v>0.0595870790498948</v>
       </c>
       <c r="M24" t="n">
-        <v>4.102110422203983</v>
+        <v>4.097975207714398</v>
       </c>
       <c r="N24" t="n">
-        <v>26.66196545886035</v>
+        <v>26.60101687645959</v>
       </c>
       <c r="O24" t="n">
-        <v>5.163522582390858</v>
+        <v>5.157617364293283</v>
       </c>
       <c r="P24" t="n">
-        <v>376.6566393096201</v>
+        <v>376.6803377774424</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34749,28 +34867,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1662066464774155</v>
+        <v>0.1642407788797459</v>
       </c>
       <c r="J25" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K25" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05870224411363412</v>
+        <v>0.05775050490302991</v>
       </c>
       <c r="M25" t="n">
-        <v>3.969118482937748</v>
+        <v>3.963860582355462</v>
       </c>
       <c r="N25" t="n">
-        <v>25.52373599032838</v>
+        <v>25.45991492868745</v>
       </c>
       <c r="O25" t="n">
-        <v>5.05210213577758</v>
+        <v>5.045781894680689</v>
       </c>
       <c r="P25" t="n">
-        <v>376.4959342352543</v>
+        <v>376.517219863002</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34827,28 +34945,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1460573641360357</v>
+        <v>0.1460193705400096</v>
       </c>
       <c r="J26" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K26" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05384966575107852</v>
+        <v>0.05421113029823021</v>
       </c>
       <c r="M26" t="n">
-        <v>3.650503744101566</v>
+        <v>3.637370427981922</v>
       </c>
       <c r="N26" t="n">
-        <v>21.597287195758</v>
+        <v>21.51847593548707</v>
       </c>
       <c r="O26" t="n">
-        <v>4.647288155016644</v>
+        <v>4.638801131271642</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5015244945342</v>
+        <v>380.5019358739897</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34905,28 +35023,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09349499611264889</v>
+        <v>0.09143101958770986</v>
       </c>
       <c r="J27" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K27" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02123212707524635</v>
+        <v>0.02044762630685104</v>
       </c>
       <c r="M27" t="n">
-        <v>3.849585598551799</v>
+        <v>3.844618268562204</v>
       </c>
       <c r="N27" t="n">
-        <v>23.21871000599354</v>
+        <v>23.16630212293042</v>
       </c>
       <c r="O27" t="n">
-        <v>4.818579666872131</v>
+        <v>4.813138489897255</v>
       </c>
       <c r="P27" t="n">
-        <v>381.0905144028911</v>
+        <v>381.1128623148471</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34983,28 +35101,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1350208820312352</v>
+        <v>0.1345191173434017</v>
       </c>
       <c r="J28" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K28" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03420413188843263</v>
+        <v>0.03420684368237004</v>
       </c>
       <c r="M28" t="n">
-        <v>4.433624088192639</v>
+        <v>4.419255611557989</v>
       </c>
       <c r="N28" t="n">
-        <v>29.66086436271538</v>
+        <v>29.55452386433399</v>
       </c>
       <c r="O28" t="n">
-        <v>5.446178877223496</v>
+        <v>5.436407257034189</v>
       </c>
       <c r="P28" t="n">
-        <v>382.9089873313376</v>
+        <v>382.9144202386071</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35061,28 +35179,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1620811957984463</v>
+        <v>0.1601626861769151</v>
       </c>
       <c r="J29" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K29" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05261151688708499</v>
+        <v>0.05175833350961534</v>
       </c>
       <c r="M29" t="n">
-        <v>4.319558366770178</v>
+        <v>4.312645874401361</v>
       </c>
       <c r="N29" t="n">
-        <v>27.25760492470136</v>
+        <v>27.18605970934758</v>
       </c>
       <c r="O29" t="n">
-        <v>5.220881623318169</v>
+        <v>5.214025288522063</v>
       </c>
       <c r="P29" t="n">
-        <v>387.0070306221156</v>
+        <v>387.027803476647</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35139,28 +35257,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.180902879741553</v>
+        <v>0.1791257522670915</v>
       </c>
       <c r="J30" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K30" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L30" t="n">
-        <v>0.08655319426319941</v>
+        <v>0.08550277824193453</v>
       </c>
       <c r="M30" t="n">
-        <v>3.542928711688016</v>
+        <v>3.536960340782642</v>
       </c>
       <c r="N30" t="n">
-        <v>19.90060467820871</v>
+        <v>19.85194425457989</v>
       </c>
       <c r="O30" t="n">
-        <v>4.461009378852359</v>
+        <v>4.455552070684383</v>
       </c>
       <c r="P30" t="n">
-        <v>384.9601444740022</v>
+        <v>384.9793864992161</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35217,28 +35335,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1203873764688665</v>
+        <v>0.1153124986664155</v>
       </c>
       <c r="J31" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K31" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03565665436844789</v>
+        <v>0.03277690279428203</v>
       </c>
       <c r="M31" t="n">
-        <v>3.866296460444822</v>
+        <v>3.874661540295824</v>
       </c>
       <c r="N31" t="n">
-        <v>22.58541879382191</v>
+        <v>22.69845721951782</v>
       </c>
       <c r="O31" t="n">
-        <v>4.752411892273428</v>
+        <v>4.764289791723192</v>
       </c>
       <c r="P31" t="n">
-        <v>383.9349523470549</v>
+        <v>383.9899010932961</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35295,28 +35413,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1733506590762699</v>
+        <v>0.1695196213292465</v>
       </c>
       <c r="J32" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K32" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06730131921673077</v>
+        <v>0.06472741414362226</v>
       </c>
       <c r="M32" t="n">
-        <v>3.818834596388358</v>
+        <v>3.82332986889568</v>
       </c>
       <c r="N32" t="n">
-        <v>23.99628052830046</v>
+        <v>24.02009512983077</v>
       </c>
       <c r="O32" t="n">
-        <v>4.898599853866455</v>
+        <v>4.901030007032275</v>
       </c>
       <c r="P32" t="n">
-        <v>395.5775663303314</v>
+        <v>395.6190472741484</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35373,28 +35491,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1126366034091789</v>
+        <v>0.1091869775444865</v>
       </c>
       <c r="J33" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K33" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01686169719623698</v>
+        <v>0.01594641180987721</v>
       </c>
       <c r="M33" t="n">
-        <v>4.763683688875945</v>
+        <v>4.764801517018657</v>
       </c>
       <c r="N33" t="n">
-        <v>42.62334925425426</v>
+        <v>42.5581058930379</v>
       </c>
       <c r="O33" t="n">
-        <v>6.528656006733258</v>
+        <v>6.523657401568379</v>
       </c>
       <c r="P33" t="n">
-        <v>378.1685725658839</v>
+        <v>378.2059237344528</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35432,7 +35550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH274"/>
+  <dimension ref="A1:AH275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82177,7 +82295,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>-36.592364598698296,175.52268826536556</t>
+          <t>-36.592362522389244,175.52273400047227</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -82308,6 +82426,178 @@
       <c r="AH274" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-36.588690588477476,175.5247586483114</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>-36.589100058671185,175.52402221255335</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>-36.58964490938032,175.52344519603</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-36.59024610187731,175.52295107361996</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-36.59094360229475,175.52272108179181</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-36.59165148220014,175.52261732659605</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-36.59235932686482,175.52280438791016</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-36.593040662702805,175.52297959916137</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-36.59374669950016,175.52301187620827</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-36.59440960125935,175.52332146234858</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-36.595070877363824,175.52364438189133</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-36.59566697547522,175.52412764591932</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-36.59626197602668,175.52459658653558</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-36.596849758953645,175.52508990712334</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-36.59740044423608,175.52564937793449</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-36.59791145217203,175.52627754771538</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>-36.5984647902895,175.52685745082587</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-36.59898228204079,175.52747492710614</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>-36.599494840290305,175.52809468058086</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>-36.59996975105787,175.52876576898066</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>-36.600473977462585,175.52940936413748</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>-36.60093926912302,175.53008496023332</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>-36.6013770180297,175.53078039966582</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>-36.60179019396228,175.53151077171293</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>-36.60215325113193,175.53227452478518</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>-36.602537290439514,175.53301903774516</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>-36.60283878887825,175.53382433441195</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>-36.60311815048945,175.5346207080568</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>-36.603343388707664,175.5354409438096</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>-36.60358647812253,175.53628126566684</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>-36.603623029119284,175.5370602935314</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>-36.60351784448872,175.53785124124764</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH275"/>
+  <dimension ref="A1:AH276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29878,7 +29878,7 @@
         <v>364.39</v>
       </c>
       <c r="H274" t="n">
-        <v>373.64</v>
+        <v>369.54</v>
       </c>
       <c r="I274" t="n">
         <v>391.74</v>
@@ -29986,7 +29986,7 @@
         <v>366.21</v>
       </c>
       <c r="H275" t="n">
-        <v>379.95</v>
+        <v>367.72</v>
       </c>
       <c r="I275" t="n">
         <v>392.98</v>
@@ -30066,6 +30066,114 @@
       <c r="AH275" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="C276" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="D276" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="E276" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="F276" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="G276" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="H276" t="n">
+        <v>353.82</v>
+      </c>
+      <c r="I276" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="J276" t="n">
+        <v>372.85</v>
+      </c>
+      <c r="K276" t="n">
+        <v>376.31</v>
+      </c>
+      <c r="L276" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="M276" t="n">
+        <v>381.23</v>
+      </c>
+      <c r="N276" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="O276" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="P276" t="n">
+        <v>378.66</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="R276" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="S276" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="T276" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="U276" t="n">
+        <v>377.53</v>
+      </c>
+      <c r="V276" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="W276" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="X276" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>384.83</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30080,7 +30188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32893,6 +33001,16 @@
       </c>
       <c r="B281" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -33061,28 +33179,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.192777130612898</v>
+        <v>-0.2038603593855934</v>
       </c>
       <c r="J2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K2" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04194428618788526</v>
+        <v>0.04618705868076101</v>
       </c>
       <c r="M2" t="n">
-        <v>5.607899131440972</v>
+        <v>5.651209825045563</v>
       </c>
       <c r="N2" t="n">
-        <v>47.74035009637576</v>
+        <v>48.46138124315361</v>
       </c>
       <c r="O2" t="n">
-        <v>6.909439202741114</v>
+        <v>6.961420921274162</v>
       </c>
       <c r="P2" t="n">
-        <v>380.5408294606603</v>
+        <v>380.6642504892424</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33139,28 +33257,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2433920743908323</v>
+        <v>-0.2487764415984723</v>
       </c>
       <c r="J3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0657509648353648</v>
+        <v>0.06869122790420279</v>
       </c>
       <c r="M3" t="n">
-        <v>5.467341625549576</v>
+        <v>5.473348621485306</v>
       </c>
       <c r="N3" t="n">
-        <v>47.99296968721113</v>
+        <v>48.03204056499431</v>
       </c>
       <c r="O3" t="n">
-        <v>6.92769584257357</v>
+        <v>6.930515173130661</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2522193549098</v>
+        <v>374.3116250219086</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33217,28 +33335,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3699678262745729</v>
+        <v>-0.3724361757378596</v>
       </c>
       <c r="J4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K4" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1016704682896091</v>
+        <v>0.1035431152801582</v>
       </c>
       <c r="M4" t="n">
-        <v>6.368320072325582</v>
+        <v>6.356540957814809</v>
       </c>
       <c r="N4" t="n">
-        <v>68.01823957296433</v>
+        <v>67.81085329068641</v>
       </c>
       <c r="O4" t="n">
-        <v>8.247317113641522</v>
+        <v>8.234734561033914</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7688552270701</v>
+        <v>370.7963423642489</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33295,28 +33413,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6284925691143897</v>
+        <v>-0.6347183454658014</v>
       </c>
       <c r="J5" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K5" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1770737204312527</v>
+        <v>0.180696852095263</v>
       </c>
       <c r="M5" t="n">
-        <v>7.827341444086978</v>
+        <v>7.826966260422432</v>
       </c>
       <c r="N5" t="n">
-        <v>102.6973377392519</v>
+        <v>102.597161637114</v>
       </c>
       <c r="O5" t="n">
-        <v>10.13396949567404</v>
+        <v>10.12902570028895</v>
       </c>
       <c r="P5" t="n">
-        <v>384.780840562451</v>
+        <v>384.8504861260483</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33373,28 +33491,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5884180253244361</v>
+        <v>-0.5932834721021024</v>
       </c>
       <c r="J6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K6" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1229785145478377</v>
+        <v>0.1254708774222414</v>
       </c>
       <c r="M6" t="n">
-        <v>9.158793262384856</v>
+        <v>9.148704236225832</v>
       </c>
       <c r="N6" t="n">
-        <v>139.2950720005556</v>
+        <v>138.9547298665879</v>
       </c>
       <c r="O6" t="n">
-        <v>11.8023333286497</v>
+        <v>11.78790608490702</v>
       </c>
       <c r="P6" t="n">
-        <v>383.626501390466</v>
+        <v>383.680520393157</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33451,28 +33569,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6910098208626974</v>
+        <v>-0.688765919727362</v>
       </c>
       <c r="J7" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K7" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05814227441823439</v>
+        <v>0.05820301544153339</v>
       </c>
       <c r="M7" t="n">
-        <v>16.42574336379369</v>
+        <v>16.37404963586664</v>
       </c>
       <c r="N7" t="n">
-        <v>433.3740211553821</v>
+        <v>431.7996130838692</v>
       </c>
       <c r="O7" t="n">
-        <v>20.81763726159581</v>
+        <v>20.77978857168353</v>
       </c>
       <c r="P7" t="n">
-        <v>383.5906980064905</v>
+        <v>383.5656209124166</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -33533,28 +33651,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4417574239094302</v>
+        <v>0.4143351002120836</v>
       </c>
       <c r="J8" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K8" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03116059142782623</v>
+        <v>0.02754916903410065</v>
       </c>
       <c r="M8" t="n">
-        <v>14.41694323289631</v>
+        <v>14.45335588399714</v>
       </c>
       <c r="N8" t="n">
-        <v>342.8777512665547</v>
+        <v>343.7825531945992</v>
       </c>
       <c r="O8" t="n">
-        <v>18.5169584777456</v>
+        <v>18.54137409132881</v>
       </c>
       <c r="P8" t="n">
-        <v>364.2751637512083</v>
+        <v>364.5802151155264</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33615,28 +33733,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6491001145773249</v>
+        <v>0.652993306385295</v>
       </c>
       <c r="J9" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1327069242904367</v>
+        <v>0.1348918879375187</v>
       </c>
       <c r="M9" t="n">
-        <v>9.848503486620459</v>
+        <v>9.83471319185959</v>
       </c>
       <c r="N9" t="n">
-        <v>158.9991534164197</v>
+        <v>158.5229718507001</v>
       </c>
       <c r="O9" t="n">
-        <v>12.60948664365127</v>
+        <v>12.59059060769987</v>
       </c>
       <c r="P9" t="n">
-        <v>370.086482381261</v>
+        <v>370.0438029939149</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33697,28 +33815,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3871041018829771</v>
+        <v>0.3794749164658401</v>
       </c>
       <c r="J10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K10" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1006841396775618</v>
+        <v>0.09730491861956958</v>
       </c>
       <c r="M10" t="n">
-        <v>6.874829415025406</v>
+        <v>6.884688288615145</v>
       </c>
       <c r="N10" t="n">
-        <v>77.10722255897545</v>
+        <v>77.26443800754355</v>
       </c>
       <c r="O10" t="n">
-        <v>8.781071834290815</v>
+        <v>8.7900192268017</v>
       </c>
       <c r="P10" t="n">
-        <v>373.3554495242441</v>
+        <v>373.4388832416757</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33775,28 +33893,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3620571883791854</v>
+        <v>0.3566971316287771</v>
       </c>
       <c r="J11" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K11" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1178235144690056</v>
+        <v>0.1151529842508194</v>
       </c>
       <c r="M11" t="n">
-        <v>5.954110301018113</v>
+        <v>5.956311978361528</v>
       </c>
       <c r="N11" t="n">
-        <v>55.34910405083112</v>
+        <v>55.35548920577833</v>
       </c>
       <c r="O11" t="n">
-        <v>7.439697846742912</v>
+        <v>7.440126961670636</v>
       </c>
       <c r="P11" t="n">
-        <v>374.0738508106514</v>
+        <v>374.133371301545</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33853,28 +33971,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3877890591047973</v>
+        <v>0.3801468480143368</v>
       </c>
       <c r="J12" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K12" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1371589884010735</v>
+        <v>0.1324776766947062</v>
       </c>
       <c r="M12" t="n">
-        <v>5.91579666890244</v>
+        <v>5.931960005249138</v>
       </c>
       <c r="N12" t="n">
-        <v>53.34949974910959</v>
+        <v>53.58080198755103</v>
       </c>
       <c r="O12" t="n">
-        <v>7.30407418836293</v>
+        <v>7.319890845330348</v>
       </c>
       <c r="P12" t="n">
-        <v>371.7012074672036</v>
+        <v>371.7860700305679</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33931,28 +34049,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3136166057377252</v>
+        <v>0.3118023283254643</v>
       </c>
       <c r="J13" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K13" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1251701478352502</v>
+        <v>0.1246744293017104</v>
       </c>
       <c r="M13" t="n">
-        <v>4.95857831936241</v>
+        <v>4.949461165023405</v>
       </c>
       <c r="N13" t="n">
-        <v>38.76623918407044</v>
+        <v>38.64732155418881</v>
       </c>
       <c r="O13" t="n">
-        <v>6.226254025019412</v>
+        <v>6.21669699713512</v>
       </c>
       <c r="P13" t="n">
-        <v>375.2829483718678</v>
+        <v>375.3030949276271</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34009,28 +34127,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1428893091980658</v>
+        <v>0.1441610362554825</v>
       </c>
       <c r="J14" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K14" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04139862797263183</v>
+        <v>0.04240043972892893</v>
       </c>
       <c r="M14" t="n">
-        <v>4.144380645068824</v>
+        <v>4.136490515101809</v>
       </c>
       <c r="N14" t="n">
-        <v>26.82562274306082</v>
+        <v>26.73894652470722</v>
       </c>
       <c r="O14" t="n">
-        <v>5.179345783307078</v>
+        <v>5.170971526193818</v>
       </c>
       <c r="P14" t="n">
-        <v>377.9949873947357</v>
+        <v>377.9809362661864</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34087,28 +34205,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2686288939334827</v>
+        <v>0.2683740376316517</v>
       </c>
       <c r="J15" t="n">
+        <v>275</v>
+      </c>
+      <c r="K15" t="n">
         <v>274</v>
       </c>
-      <c r="K15" t="n">
-        <v>273</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1614020298348058</v>
+        <v>0.1621745975723113</v>
       </c>
       <c r="M15" t="n">
-        <v>3.677756746930231</v>
+        <v>3.665171848583946</v>
       </c>
       <c r="N15" t="n">
-        <v>21.7231376678248</v>
+        <v>21.64435020839034</v>
       </c>
       <c r="O15" t="n">
-        <v>4.660808692472241</v>
+        <v>4.65234889151602</v>
       </c>
       <c r="P15" t="n">
-        <v>374.1904406994901</v>
+        <v>374.1932142432761</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34165,28 +34283,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1575298121436168</v>
+        <v>0.1571795386559684</v>
       </c>
       <c r="J16" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K16" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07654335927935119</v>
+        <v>0.07676456459357317</v>
       </c>
       <c r="M16" t="n">
-        <v>3.465028902786704</v>
+        <v>3.453881465763415</v>
       </c>
       <c r="N16" t="n">
-        <v>17.31886109884745</v>
+        <v>17.25681362264818</v>
       </c>
       <c r="O16" t="n">
-        <v>4.161593576846188</v>
+        <v>4.154132114250602</v>
       </c>
       <c r="P16" t="n">
-        <v>374.8877032304068</v>
+        <v>374.891514243172</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34243,28 +34361,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2006328419461929</v>
+        <v>0.2020482912073715</v>
       </c>
       <c r="J17" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K17" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1112084966022374</v>
+        <v>0.1132883841989772</v>
       </c>
       <c r="M17" t="n">
-        <v>3.420921472519328</v>
+        <v>3.416433729203816</v>
       </c>
       <c r="N17" t="n">
-        <v>18.61018982075112</v>
+        <v>18.55770615435842</v>
       </c>
       <c r="O17" t="n">
-        <v>4.313952922871449</v>
+        <v>4.307865614705085</v>
       </c>
       <c r="P17" t="n">
-        <v>372.4642971507162</v>
+        <v>372.4488969123511</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34321,28 +34439,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1255495072255819</v>
+        <v>0.1251463322816697</v>
       </c>
       <c r="J18" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K18" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04219975625720063</v>
+        <v>0.04224580143981582</v>
       </c>
       <c r="M18" t="n">
-        <v>3.639446640362716</v>
+        <v>3.627796712713741</v>
       </c>
       <c r="N18" t="n">
-        <v>20.69568731461187</v>
+        <v>20.62166266252508</v>
       </c>
       <c r="O18" t="n">
-        <v>4.549251291653592</v>
+        <v>4.541108087518407</v>
       </c>
       <c r="P18" t="n">
-        <v>374.5380897072196</v>
+        <v>374.5424762934501</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34399,28 +34517,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1264864019615998</v>
+        <v>0.1248825967536995</v>
       </c>
       <c r="J19" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K19" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03983586224232993</v>
+        <v>0.03912420167739949</v>
       </c>
       <c r="M19" t="n">
-        <v>3.66082901248017</v>
+        <v>3.652322069661669</v>
       </c>
       <c r="N19" t="n">
-        <v>22.30713343829126</v>
+        <v>22.24551796674399</v>
       </c>
       <c r="O19" t="n">
-        <v>4.72304281563181</v>
+        <v>4.716515447525216</v>
       </c>
       <c r="P19" t="n">
-        <v>376.9173254018838</v>
+        <v>376.9347749729637</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34477,28 +34595,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09087288170480658</v>
+        <v>0.0883132215862204</v>
       </c>
       <c r="J20" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K20" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02184421011569793</v>
+        <v>0.02076356518521449</v>
       </c>
       <c r="M20" t="n">
-        <v>3.643100591905931</v>
+        <v>3.640043980642454</v>
       </c>
       <c r="N20" t="n">
-        <v>21.39070575998541</v>
+        <v>21.36259509142937</v>
       </c>
       <c r="O20" t="n">
-        <v>4.625008730800992</v>
+        <v>4.621968746262718</v>
       </c>
       <c r="P20" t="n">
-        <v>377.9938138668526</v>
+        <v>378.0216632409285</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34555,28 +34673,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1502815588250687</v>
+        <v>0.1493139770753698</v>
       </c>
       <c r="J21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05754547355257755</v>
+        <v>0.05724142591492776</v>
       </c>
       <c r="M21" t="n">
-        <v>3.603422473008521</v>
+        <v>3.594353131070679</v>
       </c>
       <c r="N21" t="n">
-        <v>21.39663347288232</v>
+        <v>21.32592555566417</v>
       </c>
       <c r="O21" t="n">
-        <v>4.625649519027823</v>
+        <v>4.618000168434835</v>
       </c>
       <c r="P21" t="n">
-        <v>374.8522033226411</v>
+        <v>374.8627307148917</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34633,28 +34751,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1963290918099213</v>
+        <v>0.1938720569203564</v>
       </c>
       <c r="J22" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K22" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08164900811564002</v>
+        <v>0.08020710349107041</v>
       </c>
       <c r="M22" t="n">
-        <v>4.059255844659524</v>
+        <v>4.055379434723775</v>
       </c>
       <c r="N22" t="n">
-        <v>25.07909900078907</v>
+        <v>25.0336726756231</v>
       </c>
       <c r="O22" t="n">
-        <v>5.00790365330535</v>
+        <v>5.003366134476179</v>
       </c>
       <c r="P22" t="n">
-        <v>374.0767674104923</v>
+        <v>374.1035002111716</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34711,28 +34829,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1813746587773797</v>
+        <v>0.1786843847422184</v>
       </c>
       <c r="J23" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K23" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0764340119285345</v>
+        <v>0.07471209137580592</v>
       </c>
       <c r="M23" t="n">
-        <v>3.905362630112517</v>
+        <v>3.904375872856861</v>
       </c>
       <c r="N23" t="n">
-        <v>22.99425378900881</v>
+        <v>22.96551086358467</v>
       </c>
       <c r="O23" t="n">
-        <v>4.795232401981036</v>
+        <v>4.792234433287323</v>
       </c>
       <c r="P23" t="n">
-        <v>376.8793856085711</v>
+        <v>376.9086560759381</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34789,28 +34907,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1706960454309506</v>
+        <v>0.1682827395345159</v>
       </c>
       <c r="J24" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K24" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0595870790498948</v>
+        <v>0.05833806803347807</v>
       </c>
       <c r="M24" t="n">
-        <v>4.097975207714398</v>
+        <v>4.095219004521049</v>
       </c>
       <c r="N24" t="n">
-        <v>26.60101687645959</v>
+        <v>26.54844160808119</v>
       </c>
       <c r="O24" t="n">
-        <v>5.157617364293283</v>
+        <v>5.152517987167166</v>
       </c>
       <c r="P24" t="n">
-        <v>376.6803377774424</v>
+        <v>376.7065948020298</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34867,28 +34985,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1642407788797459</v>
+        <v>0.1621693507584901</v>
       </c>
       <c r="J25" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K25" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05775050490302991</v>
+        <v>0.05672338441044389</v>
       </c>
       <c r="M25" t="n">
-        <v>3.963860582355462</v>
+        <v>3.959287371746379</v>
       </c>
       <c r="N25" t="n">
-        <v>25.45991492868745</v>
+        <v>25.39986474708145</v>
       </c>
       <c r="O25" t="n">
-        <v>5.045781894680689</v>
+        <v>5.039827848952923</v>
       </c>
       <c r="P25" t="n">
-        <v>376.517219863002</v>
+        <v>376.5397572210681</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34945,28 +35063,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1460193705400096</v>
+        <v>0.1459320857069478</v>
       </c>
       <c r="J26" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K26" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05421113029823021</v>
+        <v>0.05454189650171959</v>
       </c>
       <c r="M26" t="n">
-        <v>3.637370427981922</v>
+        <v>3.624573194851436</v>
       </c>
       <c r="N26" t="n">
-        <v>21.51847593548707</v>
+        <v>21.44028469373891</v>
       </c>
       <c r="O26" t="n">
-        <v>4.638801131271642</v>
+        <v>4.630365503255537</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5019358739897</v>
+        <v>380.5028855422481</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35023,28 +35141,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09143101958770986</v>
+        <v>0.08921485781228325</v>
       </c>
       <c r="J27" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K27" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02044762630685104</v>
+        <v>0.01960282725385809</v>
       </c>
       <c r="M27" t="n">
-        <v>3.844618268562204</v>
+        <v>3.840238360759706</v>
       </c>
       <c r="N27" t="n">
-        <v>23.16630212293042</v>
+        <v>23.11929719102611</v>
       </c>
       <c r="O27" t="n">
-        <v>4.813138489897255</v>
+        <v>4.808253029014396</v>
       </c>
       <c r="P27" t="n">
-        <v>381.1128623148471</v>
+        <v>381.1369743904498</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35101,28 +35219,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1345191173434017</v>
+        <v>0.1333257467737932</v>
       </c>
       <c r="J28" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K28" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03420684368237004</v>
+        <v>0.03385977599515133</v>
       </c>
       <c r="M28" t="n">
-        <v>4.419255611557989</v>
+        <v>4.407423566357178</v>
       </c>
       <c r="N28" t="n">
-        <v>29.55452386433399</v>
+        <v>29.45785010692373</v>
       </c>
       <c r="O28" t="n">
-        <v>5.436407257034189</v>
+        <v>5.427508646416303</v>
       </c>
       <c r="P28" t="n">
-        <v>382.9144202386071</v>
+        <v>382.9274042372102</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35179,28 +35297,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1601626861769151</v>
+        <v>0.1574894904700979</v>
       </c>
       <c r="J29" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K29" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05175833350961534</v>
+        <v>0.0503998153802715</v>
       </c>
       <c r="M29" t="n">
-        <v>4.312645874401361</v>
+        <v>4.309191982462244</v>
       </c>
       <c r="N29" t="n">
-        <v>27.18605970934758</v>
+        <v>27.1413793837027</v>
       </c>
       <c r="O29" t="n">
-        <v>5.214025288522063</v>
+        <v>5.209738897843413</v>
       </c>
       <c r="P29" t="n">
-        <v>387.027803476647</v>
+        <v>387.0568881299868</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35257,28 +35375,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1791257522670915</v>
+        <v>0.1773322431191742</v>
       </c>
       <c r="J30" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K30" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L30" t="n">
-        <v>0.08550277824193453</v>
+        <v>0.08443552540901766</v>
       </c>
       <c r="M30" t="n">
-        <v>3.536960340782642</v>
+        <v>3.531013709522878</v>
       </c>
       <c r="N30" t="n">
-        <v>19.85194425457989</v>
+        <v>19.80414297624259</v>
       </c>
       <c r="O30" t="n">
-        <v>4.455552070684383</v>
+        <v>4.450184600243297</v>
       </c>
       <c r="P30" t="n">
-        <v>384.9793864992161</v>
+        <v>384.9989000693211</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35335,28 +35453,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1153124986664155</v>
+        <v>0.1090135184082934</v>
       </c>
       <c r="J31" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K31" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03277690279428203</v>
+        <v>0.0292373465499024</v>
       </c>
       <c r="M31" t="n">
-        <v>3.874661540295824</v>
+        <v>3.888047469441925</v>
       </c>
       <c r="N31" t="n">
-        <v>22.69845721951782</v>
+        <v>22.91673448944941</v>
       </c>
       <c r="O31" t="n">
-        <v>4.764289791723192</v>
+        <v>4.787142622635074</v>
       </c>
       <c r="P31" t="n">
-        <v>383.9899010932961</v>
+        <v>384.0584346678245</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35413,28 +35531,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1695196213292465</v>
+        <v>0.1647113245330659</v>
       </c>
       <c r="J32" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K32" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06472741414362226</v>
+        <v>0.06134882675189268</v>
       </c>
       <c r="M32" t="n">
-        <v>3.82332986889568</v>
+        <v>3.832438978025376</v>
       </c>
       <c r="N32" t="n">
-        <v>24.02009512983077</v>
+        <v>24.10803425975421</v>
       </c>
       <c r="O32" t="n">
-        <v>4.901030007032275</v>
+        <v>4.909993305469389</v>
       </c>
       <c r="P32" t="n">
-        <v>395.6190472741484</v>
+        <v>395.6713620542133</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35491,28 +35609,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1091869775444865</v>
+        <v>0.1056414938481727</v>
       </c>
       <c r="J33" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K33" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01594641180987721</v>
+        <v>0.01502232654428992</v>
       </c>
       <c r="M33" t="n">
-        <v>4.764801517018657</v>
+        <v>4.766402409813585</v>
       </c>
       <c r="N33" t="n">
-        <v>42.5581058930379</v>
+        <v>42.49865356193818</v>
       </c>
       <c r="O33" t="n">
-        <v>6.523657401568379</v>
+        <v>6.519099137299431</v>
       </c>
       <c r="P33" t="n">
-        <v>378.2059237344528</v>
+        <v>378.2444989738065</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35550,7 +35668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH275"/>
+  <dimension ref="A1:AH276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82295,7 +82413,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>-36.592362522389244,175.52273400047227</t>
+          <t>-36.592364598698296,175.52268826536556</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -82467,7 +82585,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>-36.59235932686482,175.52280438791016</t>
+          <t>-36.59236552037134,175.522667963439</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -82598,6 +82716,178 @@
       <c r="AH275" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-36.58865859069186,175.524728694351</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>-36.589083854459425,175.52400201741435</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>-36.58963545560005,175.5234284459031</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-36.59024036522588,175.52293443122244</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-36.59094547604065,175.5227323522957</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-36.59165245678339,175.5226370648951</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-36.59237255940904,175.5225129102411</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-36.59304016111515,175.52298323329128</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-36.5937526555772,175.52298854932485</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-36.594417503288504,175.52329734445073</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-36.595084001555115,175.52361192170932</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-36.59567520376519,175.52411044532298</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-36.59625796027259,175.52460360183545</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-36.59684092138658,175.52510317163163</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-36.59739246030053,175.52566000537993</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-36.597907167851865,175.5262831339567</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>-36.598459852858404,175.52686396273538</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>-36.598983553032646,175.52747334306943</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>-36.599494575399305,175.5280949836167</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>-36.599974738853675,175.52876028250571</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>-36.60047343823943,175.52940995727047</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>-36.600942826483426,175.530081353481</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>-36.60137958257365,175.5307781241463</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>-36.601791460800555,175.53150970416928</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>-36.602153711520344,175.5322741734434</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>-36.602539271562996,175.53301770877417</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>-36.60284687273322,175.53381940141784</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>-36.603127501582335,175.5346163117913</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>-36.60334373649973,175.53544082674097</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>-36.60360270847117,175.53627656360592</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>-36.603636203894666,175.53706196706125</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>-36.60351940299111,175.53785211933223</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
